--- a/event_registration_forms/003_sound_bath_registration_form--event_registration_forms.xlsx
+++ b/event_registration_forms/003_sound_bath_registration_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -834,8 +834,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -863,12 +863,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_0,_'label':_'sound_bath'}</t>
+          <t>sound_bath</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 0, 'label': 'Sound Bath'}</t>
+          <t>Sound Bath</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'reiki'}</t>
+          <t>reiki</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Reiki'}</t>
+          <t>Reiki</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_0,_'label':_'432_hz'}</t>
+          <t>432_hz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 0, 'label': '432 Hz'}</t>
+          <t>432 Hz</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'528_hz'}</t>
+          <t>528_hz</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '528 Hz'}</t>
+          <t>528 Hz</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'5280_hz'}</t>
+          <t>5280_hz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '5280 Hz'}</t>
+          <t>5280 Hz</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_0,_'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 0, 'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'stripe'}</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Stripe'}</t>
+          <t>Stripe</t>
         </is>
       </c>
     </row>
